--- a/results/perturbation/excel/perturbation_summary.xlsx
+++ b/results/perturbation/excel/perturbation_summary.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T6"/>
+  <dimension ref="A1:Z6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -529,6 +529,36 @@
           <t>stage3_variation_changed</t>
         </is>
       </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>max_residual_satisfaction</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>max_residual_floor</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>max_residual_physical</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>max_residual_satisfaction_relaxed</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>max_residual_floor_relaxed</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>max_residual_physical_relaxed</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -593,6 +623,24 @@
       <c r="T2" t="n">
         <v>200</v>
       </c>
+      <c r="U2" t="n">
+        <v>1.221245327087672e-15</v>
+      </c>
+      <c r="V2" t="n">
+        <v>7.617255715075544e-10</v>
+      </c>
+      <c r="W2" t="n">
+        <v>2.882471547399269e-11</v>
+      </c>
+      <c r="X2" t="n">
+        <v>5.551115123125783e-16</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>3.026262573868621e-10</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>2.882471547399269e-11</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -657,6 +705,24 @@
       <c r="T3" t="n">
         <v>200</v>
       </c>
+      <c r="U3" t="n">
+        <v>1.443289932012704e-15</v>
+      </c>
+      <c r="V3" t="n">
+        <v>4.495052663422427e-09</v>
+      </c>
+      <c r="W3" t="n">
+        <v>3.448383049107615e-16</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1.443289932012704e-15</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>4.495052663422427e-09</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>2.568156307844724e-16</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -721,6 +787,24 @@
       <c r="T4" t="n">
         <v>200</v>
       </c>
+      <c r="U4" t="n">
+        <v>9.992007221626409e-16</v>
+      </c>
+      <c r="V4" t="n">
+        <v>3.663757075500484e-10</v>
+      </c>
+      <c r="W4" t="n">
+        <v>2.41237111480267e-11</v>
+      </c>
+      <c r="X4" t="n">
+        <v>4.440892098500626e-16</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>2.220446049250313e-16</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2.41237111480267e-11</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -785,6 +869,24 @@
       <c r="T5" t="n">
         <v>200</v>
       </c>
+      <c r="U5" t="n">
+        <v>1.110223024625157e-15</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.011845274234702e-09</v>
+      </c>
+      <c r="W5" t="n">
+        <v>3.944495062191746e-16</v>
+      </c>
+      <c r="X5" t="n">
+        <v>9.992007221626409e-16</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.011845274234702e-09</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>1.981420775426551e-16</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -848,6 +950,24 @@
       </c>
       <c r="T6" t="n">
         <v>200</v>
+      </c>
+      <c r="U6" t="n">
+        <v>9.992007221626409e-16</v>
+      </c>
+      <c r="V6" t="n">
+        <v>4.572454526119429e-09</v>
+      </c>
+      <c r="W6" t="n">
+        <v>2.590086940628119e-11</v>
+      </c>
+      <c r="X6" t="n">
+        <v>8.881784197001252e-16</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>4.572454526119429e-09</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2.590086940628119e-11</v>
       </c>
     </row>
   </sheetData>
